--- a/Cardiotoxicity/CardioTox_Test_set 2_with_fingerprints_RDKit_CDK.xlsx
+++ b/Cardiotoxicity/CardioTox_Test_set 2_with_fingerprints_RDKit_CDK.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD42"/>
+  <dimension ref="A1:BB42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,235 +476,225 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>AMW</t>
+          <t>NumRotatableBonds</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>NumRotatableBonds</t>
+          <t>NumAromaticRings</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>NumAromaticRings</t>
+          <t>NumSaturatedRings</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>NumSaturatedRings</t>
+          <t>NumAliphaticRings</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>NumAliphaticRings</t>
+          <t>NumAromaticHeterocycles</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>NumAromaticHeterocycles</t>
+          <t>NumSaturatedHeterocycles</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>NumSaturatedHeterocycles</t>
+          <t>NumAliphaticHeterocycles</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NumAliphaticHeterocycles</t>
+          <t>NumAromaticCarbocycles</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>NumAromaticCarbocycles</t>
+          <t>NumSaturatedCarbocycles</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>NumSaturatedCarbocycles</t>
+          <t>NumAliphaticCarbocycles</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>NumAliphaticCarbocycles</t>
+          <t>FractionCSP3</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>FractionCSP3</t>
+          <t>Chi0v</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Chi0v</t>
+          <t>Chi1v</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Chi1v</t>
+          <t>Chi2v</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Chi2v</t>
+          <t>Chi3v</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Chi3v</t>
+          <t>Chi4v</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Chi4v</t>
+          <t>Chi1n</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Chi1n</t>
+          <t>Chi2n</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Chi2n</t>
+          <t>Chi3n</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Chi3n</t>
+          <t>Chi4n</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Chi4n</t>
+          <t>HallKierAlpha</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>HallKierAlpha</t>
+          <t>HeavyAtomCount</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>HeavyAtomCount</t>
+          <t>RingCount</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>RingCount</t>
+          <t>NumHDonors</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>NumHDonors</t>
+          <t>NumHAcceptors</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>NumHAcceptors</t>
+          <t>ALogP</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>ALogP</t>
+          <t>ALogp2</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>ALogp2</t>
+          <t>AMR</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>AMR</t>
+          <t>MLogP</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>MLogP</t>
+          <t>nAtomP</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>nAtomP</t>
+          <t>naAromAtom</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>naAromAtom</t>
+          <t>bpol</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>bpol</t>
+          <t>nB</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>nB</t>
+          <t>ECCEN</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>ECCEN</t>
+          <t>fragC</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>fragC</t>
+          <t>nHBAcc</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>nHBAcc</t>
+          <t>nHBDon</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>nHBDon</t>
+          <t>nAtomLAC</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>nAtomLAC</t>
+          <t>nAtomLC</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>nAtomLC</t>
+          <t>PetitjeanNumber</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>PetitjeanNumber</t>
+          <t>nRotB</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>nRotB</t>
+          <t>LipinskiFailures</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>LipinskiFailures</t>
+          <t>VAdjMat</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>TopoPSA</t>
+          <t>XLogP</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>VAdjMat</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>XLogP</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Fsp3</t>
         </is>
@@ -747,144 +737,138 @@
         <v>43.2</v>
       </c>
       <c r="J2" t="n">
-        <v>375.8710000000002</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="U2" t="n">
+        <v>15.38308299532353</v>
+      </c>
+      <c r="V2" t="n">
+        <v>9.335737768922536</v>
+      </c>
+      <c r="W2" t="n">
+        <v>7.350176897921855</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.361145602097039</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.564684572244015</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8.957773295913309</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>6.91374111744987</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5.109169286757554</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.438696414574272</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2.430600000000002</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>5.907816360000009</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>99.6935</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>29.704761</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>721</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1951.05</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="AX2" t="n">
         <v>6</v>
       </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.3809523809523809</v>
-      </c>
-      <c r="V2" t="n">
-        <v>15.38308299532353</v>
-      </c>
-      <c r="W2" t="n">
-        <v>9.335737768922536</v>
-      </c>
-      <c r="X2" t="n">
-        <v>7.350176897921855</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>5.361145602097039</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.564684572244015</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>8.957773295913309</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>6.91374111744987</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>5.109169286757554</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.438696414574272</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2.430600000000002</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>5.907816360000009</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>99.6935</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>29.704761</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>721</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1951.05</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.4705882352941176</v>
-      </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>5.807354922057604</v>
       </c>
       <c r="BA2" t="n">
-        <v>37.3</v>
+        <v>4.02</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.807354922057604</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="BD2" t="n">
         <v>0.3809523809523809</v>
       </c>
     </row>
@@ -925,144 +909,138 @@
         <v>18.26</v>
       </c>
       <c r="J3" t="n">
-        <v>314.498</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14.4806149030278</v>
+      </c>
+      <c r="V3" t="n">
+        <v>10.10786078013632</v>
+      </c>
+      <c r="W3" t="n">
+        <v>8.036936684022864</v>
+      </c>
+      <c r="X3" t="n">
+        <v>6.507471029956461</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.667486859754431</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8.714013930018965</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>7.126253081499903</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5.702733175832096</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.954590320136499</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF3" t="n">
         <v>4</v>
       </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.631578947368421</v>
-      </c>
-      <c r="V3" t="n">
-        <v>14.4806149030278</v>
-      </c>
-      <c r="W3" t="n">
-        <v>10.10786078013632</v>
-      </c>
-      <c r="X3" t="n">
-        <v>8.036936684022864</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>6.507471029956461</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5.667486859754431</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>8.714013930018965</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7.126253081499903</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5.702733175832096</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>4.954590320136499</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>22</v>
-      </c>
       <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2.029999999999998</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>4.12089999999999</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>93.8661</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>34.00338199999999</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>358</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2139.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AX3" t="n">
         <v>4</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2.029999999999998</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>4.12089999999999</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>93.8661</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>34.00338199999999</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>358</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2139.03</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0.4444444444444444</v>
-      </c>
       <c r="AY3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>5.643856189774724</v>
       </c>
       <c r="BA3" t="n">
-        <v>37.66</v>
+        <v>3.451000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.643856189774724</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.451000000000001</v>
-      </c>
-      <c r="BD3" t="n">
         <v>0.631578947368421</v>
       </c>
     </row>
@@ -1103,144 +1081,138 @@
         <v>32.2</v>
       </c>
       <c r="J4" t="n">
-        <v>469.6690000000001</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.40625</v>
       </c>
       <c r="U4" t="n">
-        <v>0.40625</v>
+        <v>21.45106195176754</v>
       </c>
       <c r="V4" t="n">
-        <v>21.45106195176754</v>
+        <v>13.01434661487594</v>
       </c>
       <c r="W4" t="n">
+        <v>10.73256931483735</v>
+      </c>
+      <c r="X4" t="n">
+        <v>7.018862944602727</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.830338944867121</v>
+      </c>
+      <c r="Z4" t="n">
         <v>13.01434661487594</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
         <v>10.73256931483735</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>7.018862944602727</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
         <v>4.830338944867121</v>
       </c>
-      <c r="AA4" t="n">
-        <v>13.01434661487594</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>10.73256931483735</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.018862944602727</v>
-      </c>
       <c r="AD4" t="n">
-        <v>4.830338944867121</v>
+        <v>-2.749999999999999</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2.749999999999999</v>
+        <v>35</v>
       </c>
       <c r="AF4" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.125599999999999</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>26.27177535999999</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>142.4826</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>47.48907299999999</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1151</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4739.03</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
         <v>4</v>
       </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>5.125599999999999</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>26.27177535999999</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>142.4826</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>47.48907299999999</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1151</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4739.03</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>0.4736842105263157</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.4736842105263157</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1</v>
+        <v>6.247927513443585</v>
       </c>
       <c r="BA4" t="n">
-        <v>26.3</v>
+        <v>7.394999999999998</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.247927513443585</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>7.394999999999998</v>
-      </c>
-      <c r="BD4" t="n">
         <v>0.40625</v>
       </c>
     </row>
@@ -1281,144 +1253,138 @@
         <v>18.37</v>
       </c>
       <c r="J5" t="n">
-        <v>366.5490000000002</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>16.88773296123167</v>
+      </c>
+      <c r="V5" t="n">
+        <v>10.37843302616415</v>
+      </c>
+      <c r="W5" t="n">
+        <v>8.029873732254705</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5.187211325353032</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.77836681313545</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10.37843302616415</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>8.029873732254705</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5.187211325353032</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.77836681313545</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1.839999999999999</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3.8079</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>14.50010241</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>112.2182</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>43.04503799999999</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>538</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3267.03</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX5" t="n">
         <v>10</v>
       </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>16.88773296123167</v>
-      </c>
-      <c r="W5" t="n">
-        <v>10.37843302616415</v>
-      </c>
-      <c r="X5" t="n">
-        <v>8.029873732254705</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>5.187211325353032</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.77836681313545</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>10.37843302616415</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8.029873732254705</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.187211325353032</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.77836681313545</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-1.839999999999999</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>3.8079</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>14.50010241</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>112.2182</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>43.04503799999999</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>538</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>3267.03</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1</v>
+        <v>5.857980995127573</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.47</v>
+        <v>5.225</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.857980995127573</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.225</v>
-      </c>
-      <c r="BD5" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1459,144 +1425,138 @@
         <v>52.43000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>289.3750000000001</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="U6" t="n">
+        <v>12.44261010056702</v>
+      </c>
+      <c r="V6" t="n">
+        <v>7.769561596830123</v>
+      </c>
+      <c r="W6" t="n">
+        <v>6.226609618478852</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5.006836850664758</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.705569432943791</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7.769561596830123</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6.226609618478852</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>5.006836850664758</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.705569432943791</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
         <v>4</v>
       </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="V6" t="n">
-        <v>12.44261010056702</v>
-      </c>
-      <c r="W6" t="n">
-        <v>7.769561596830123</v>
-      </c>
-      <c r="X6" t="n">
-        <v>6.226609618478852</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>5.006836850664758</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.705569432943791</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>7.769561596830123</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>6.226609618478852</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.006836850664758</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.705569432943791</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1</v>
-      </c>
       <c r="AI6" t="n">
-        <v>4</v>
+        <v>0.2641000000000004</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2641000000000004</v>
+        <v>0.0697488100000002</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0697488100000002</v>
+        <v>77.91760000000001</v>
       </c>
       <c r="AL6" t="n">
-        <v>77.91760000000001</v>
+        <v>2.89</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.89</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
         <v>6</v>
       </c>
       <c r="AO6" t="n">
-        <v>6</v>
+        <v>29.997761</v>
       </c>
       <c r="AP6" t="n">
-        <v>29.997761</v>
+        <v>23</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23</v>
+        <v>393</v>
       </c>
       <c r="AR6" t="n">
-        <v>393</v>
+        <v>1696.04</v>
       </c>
       <c r="AS6" t="n">
-        <v>1696.04</v>
+        <v>3</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="AX6" t="n">
         <v>5</v>
       </c>
-      <c r="AX6" t="n">
-        <v>0.4545454545454545</v>
-      </c>
       <c r="AY6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>5.523561956057013</v>
       </c>
       <c r="BA6" t="n">
-        <v>46.53</v>
+        <v>1.828</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.523561956057013</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.828</v>
-      </c>
-      <c r="BD6" t="n">
         <v>0.5882352941176471</v>
       </c>
     </row>
@@ -1637,144 +1597,138 @@
         <v>48.25</v>
       </c>
       <c r="J7" t="n">
-        <v>324.4240000000001</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14.05892567479274</v>
+      </c>
+      <c r="V7" t="n">
+        <v>8.682990361275793</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6.97439365893587</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.819484376609593</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.44430603425086</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8.682990361275793</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6.97439365893587</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>5.819484376609593</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.44430603425086</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
         <v>4</v>
       </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="V7" t="n">
-        <v>14.05892567479274</v>
-      </c>
-      <c r="W7" t="n">
-        <v>8.682990361275793</v>
-      </c>
-      <c r="X7" t="n">
-        <v>6.97439365893587</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>5.819484376609593</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.44430603425086</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>8.682990361275793</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>6.97439365893587</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.819484376609593</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>4.44430603425086</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1</v>
-      </c>
       <c r="AI7" t="n">
+        <v>1.276699999999999</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.629962889999997</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>91.7946</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>31.45296799999999</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>483</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2049.04</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX7" t="n">
         <v>4</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>1.276699999999999</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.629962889999997</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>91.7946</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>31.45296799999999</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>483</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2049.04</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AY7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>5.754887502163469</v>
       </c>
       <c r="BA7" t="n">
-        <v>42.35000000000001</v>
+        <v>2.604</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.754887502163469</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.604</v>
-      </c>
-      <c r="BD7" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -1815,10 +1769,10 @@
         <v>77.92000000000002</v>
       </c>
       <c r="J8" t="n">
-        <v>457.9620000000003</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -1827,132 +1781,126 @@
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4347826086956522</v>
+        <v>19.00011918292537</v>
       </c>
       <c r="V8" t="n">
-        <v>19.00011918292537</v>
+        <v>11.29754986381345</v>
       </c>
       <c r="W8" t="n">
-        <v>11.29754986381345</v>
+        <v>8.627536714061302</v>
       </c>
       <c r="X8" t="n">
-        <v>8.627536714061302</v>
+        <v>6.071609317094301</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.071609317094301</v>
+        <v>3.958589531614307</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.958589531614307</v>
+        <v>10.91958539080422</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.91958539080422</v>
+        <v>8.191100933589318</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.191100933589318</v>
+        <v>5.819633001754815</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.819633001754815</v>
+        <v>3.832601373944565</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.832601373944565</v>
+        <v>-2.679999999999999</v>
       </c>
       <c r="AE8" t="n">
-        <v>-2.679999999999999</v>
+        <v>32</v>
       </c>
       <c r="AF8" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.8039000000000026</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.6462552100000042</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>119.1909</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>42.78179599999999</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>35</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1093</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2977.09</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
         <v>4</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.8039000000000026</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.6462552100000042</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>119.1909</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>42.78179599999999</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>35</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1093</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2977.09</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
       </c>
       <c r="AV8" t="n">
         <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>0.4761904761904761</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.4761904761904761</v>
+        <v>8</v>
       </c>
       <c r="AY8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>6.129283016944966</v>
       </c>
       <c r="BA8" t="n">
-        <v>66.12</v>
+        <v>2.772</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.129283016944966</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.772</v>
-      </c>
-      <c r="BD8" t="n">
         <v>0.4347826086956521</v>
       </c>
     </row>
@@ -1993,144 +1941,138 @@
         <v>9.140000000000002</v>
       </c>
       <c r="J9" t="n">
-        <v>318.8730000000001</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="U9" t="n">
+        <v>13.91583770930621</v>
+      </c>
+      <c r="V9" t="n">
+        <v>8.331172040341192</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7.010513420734169</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.940160423539641</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.830862072909589</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7.136710986404238</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.490300683775358</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.574794941917979</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.588411696505555</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3.2828</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>10.77677584</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>90.8583</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>27.430933</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>332</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1344.04</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AX9" t="n">
         <v>4</v>
       </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="V9" t="n">
-        <v>13.91583770930621</v>
-      </c>
-      <c r="W9" t="n">
-        <v>8.331172040341192</v>
-      </c>
-      <c r="X9" t="n">
-        <v>7.010513420734169</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>4.940160423539641</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.830862072909589</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>7.136710986404238</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>5.490300683775358</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.574794941917979</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.588411696505555</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>3.2828</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>10.77677584</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>90.8583</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>27.430933</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>332</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1344.04</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0.4444444444444444</v>
-      </c>
       <c r="AY9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>5.523561956057013</v>
       </c>
       <c r="BA9" t="n">
-        <v>28.54</v>
+        <v>4.923</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.523561956057013</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.923</v>
-      </c>
-      <c r="BD9" t="n">
         <v>0.2941176470588235</v>
       </c>
     </row>
@@ -2171,144 +2113,138 @@
         <v>26.21</v>
       </c>
       <c r="J10" t="n">
-        <v>336.479</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4090909090909091</v>
+        <v>15.1032759108555</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1032759108555</v>
+        <v>9.410297276876303</v>
       </c>
       <c r="W10" t="n">
+        <v>6.761256502983478</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5.08728883763743</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.650415140649692</v>
+      </c>
+      <c r="Z10" t="n">
         <v>9.410297276876303</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
         <v>6.761256502983478</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>5.08728883763743</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AC10" t="n">
         <v>3.650415140649692</v>
       </c>
-      <c r="AA10" t="n">
-        <v>9.410297276876303</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>6.761256502983478</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5.08728883763743</v>
-      </c>
       <c r="AD10" t="n">
-        <v>3.650415140649692</v>
+        <v>-2.129999999999999</v>
       </c>
       <c r="AE10" t="n">
-        <v>-2.129999999999999</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>2</v>
+        <v>2.381600000000004</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.381600000000004</v>
+        <v>5.672018560000016</v>
       </c>
       <c r="AK10" t="n">
-        <v>5.672018560000016</v>
+        <v>100.5841</v>
       </c>
       <c r="AL10" t="n">
-        <v>100.5841</v>
+        <v>3.55</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.55</v>
+        <v>9</v>
       </c>
       <c r="AN10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
-        <v>12</v>
+        <v>35.527796</v>
       </c>
       <c r="AP10" t="n">
-        <v>35.527796</v>
+        <v>27</v>
       </c>
       <c r="AQ10" t="n">
-        <v>27</v>
+        <v>583</v>
       </c>
       <c r="AR10" t="n">
-        <v>583</v>
+        <v>2425.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>2425.03</v>
+        <v>2</v>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW10" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="AY10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>5.754887502163469</v>
       </c>
       <c r="BA10" t="n">
-        <v>20.31</v>
+        <v>3.935000000000001</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.754887502163469</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.935000000000001</v>
-      </c>
-      <c r="BD10" t="n">
         <v>0.4090909090909091</v>
       </c>
     </row>
@@ -2349,13 +2285,13 @@
         <v>47.22000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>377.3080000000002</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
@@ -2373,120 +2309,114 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4705882352941176</v>
+        <v>13.40195636443918</v>
       </c>
       <c r="V11" t="n">
-        <v>13.40195636443918</v>
+        <v>8.015356523476727</v>
       </c>
       <c r="W11" t="n">
+        <v>6.208129660705121</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.422058799036913</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.172007479174376</v>
+      </c>
+      <c r="Z11" t="n">
         <v>8.015356523476727</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
         <v>6.208129660705121</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>4.422058799036913</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
         <v>3.172007479174376</v>
       </c>
-      <c r="AA11" t="n">
-        <v>8.015356523476727</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>6.208129660705121</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.422058799036913</v>
-      </c>
       <c r="AD11" t="n">
-        <v>3.172007479174376</v>
+        <v>-1.87</v>
       </c>
       <c r="AE11" t="n">
-        <v>-1.87</v>
+        <v>26</v>
       </c>
       <c r="AF11" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>2</v>
+        <v>3.2788</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.2788</v>
+        <v>10.75052944</v>
       </c>
       <c r="AK11" t="n">
-        <v>10.75052944</v>
+        <v>79.2766</v>
       </c>
       <c r="AL11" t="n">
-        <v>79.2766</v>
+        <v>2.34</v>
       </c>
       <c r="AM11" t="n">
-        <v>2.34</v>
+        <v>10</v>
       </c>
       <c r="AN11" t="n">
         <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>10</v>
+        <v>26.25610499999999</v>
       </c>
       <c r="AP11" t="n">
-        <v>26.25610499999999</v>
+        <v>28</v>
       </c>
       <c r="AQ11" t="n">
-        <v>28</v>
+        <v>434</v>
       </c>
       <c r="AR11" t="n">
-        <v>434</v>
+        <v>1199.09</v>
       </c>
       <c r="AS11" t="n">
-        <v>1199.09</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW11" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="AY11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>5.807354922057604</v>
       </c>
       <c r="BA11" t="n">
-        <v>33.12</v>
+        <v>3.983000000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.807354922057604</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.983000000000001</v>
-      </c>
-      <c r="BD11" t="n">
         <v>0.4705882352941176</v>
       </c>
     </row>
@@ -2527,144 +2457,138 @@
         <v>9.140000000000002</v>
       </c>
       <c r="J12" t="n">
-        <v>280.415</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="U12" t="n">
+        <v>13.04876325044966</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7.835903638099349</v>
+      </c>
+      <c r="W12" t="n">
+        <v>6.065891941848764</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4.215547540145039</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.156168944332008</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7.835903638099349</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6.065891941848764</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.215547540145039</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.156168944332008</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-1.799999999999999</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.930799999999998</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>8.589588639999988</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>87.7076</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>30.19696799999999</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>331</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1789.02</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AX12" t="n">
         <v>4</v>
       </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.3684210526315789</v>
-      </c>
-      <c r="V12" t="n">
-        <v>13.04876325044966</v>
-      </c>
-      <c r="W12" t="n">
-        <v>7.835903638099349</v>
-      </c>
-      <c r="X12" t="n">
-        <v>6.065891941848764</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>4.215547540145039</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.156168944332008</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>7.835903638099349</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>6.065891941848764</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.215547540145039</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.156168944332008</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-1.799999999999999</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.930799999999998</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>8.589588639999988</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>87.7076</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>30.19696799999999</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>331</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1789.02</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0.4444444444444444</v>
-      </c>
       <c r="AY12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>5.523561956057013</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.24</v>
+        <v>4.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.523561956057013</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="BD12" t="n">
         <v>0.3684210526315789</v>
       </c>
     </row>
@@ -2705,10 +2629,10 @@
         <v>52.23</v>
       </c>
       <c r="J13" t="n">
-        <v>335.451</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -2717,10 +2641,10 @@
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -2729,120 +2653,114 @@
         <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3809523809523809</v>
+        <v>14.47351939885858</v>
       </c>
       <c r="V13" t="n">
-        <v>14.47351939885858</v>
+        <v>9.082638848606241</v>
       </c>
       <c r="W13" t="n">
+        <v>7.479578243319907</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5.350486231870673</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>4.332543774057592</v>
+      </c>
+      <c r="Z13" t="n">
         <v>9.082638848606241</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
         <v>7.479578243319907</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>5.350486231870673</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AC13" t="n">
         <v>4.332543774057592</v>
       </c>
-      <c r="AA13" t="n">
-        <v>9.082638848606241</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7.479578243319907</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>5.350486231870673</v>
-      </c>
       <c r="AD13" t="n">
-        <v>4.332543774057592</v>
+        <v>-2.329999999999999</v>
       </c>
       <c r="AE13" t="n">
-        <v>-2.329999999999999</v>
+        <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.775499999999999</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.6014002499999984</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>99.0575</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>31.588175</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>618</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2209.04</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="AX13" t="n">
         <v>4</v>
       </c>
-      <c r="AH13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.775499999999999</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0.6014002499999984</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>99.0575</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>31.588175</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>618</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2209.04</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0.4666666666666667</v>
-      </c>
       <c r="AY13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>5.807354922057604</v>
       </c>
       <c r="BA13" t="n">
-        <v>46.33000000000001</v>
+        <v>2.717000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.807354922057604</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.717000000000001</v>
-      </c>
-      <c r="BD13" t="n">
         <v>0.3809523809523809</v>
       </c>
     </row>
@@ -2883,10 +2801,10 @@
         <v>61.66000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>413.3380000000001</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
@@ -2895,10 +2813,10 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -2907,120 +2825,114 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5882352941176471</v>
+        <v>14.69889385001125</v>
       </c>
       <c r="V14" t="n">
-        <v>14.69889385001125</v>
+        <v>8.513233404097234</v>
       </c>
       <c r="W14" t="n">
+        <v>6.231482547289009</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.820492047588267</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.556195446106365</v>
+      </c>
+      <c r="Z14" t="n">
         <v>8.513233404097234</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AA14" t="n">
         <v>6.231482547289009</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AB14" t="n">
         <v>3.820492047588267</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AC14" t="n">
         <v>2.556195446106365</v>
       </c>
-      <c r="AA14" t="n">
-        <v>8.513233404097234</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>6.231482547289009</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.820492047588267</v>
-      </c>
       <c r="AD14" t="n">
-        <v>2.556195446106365</v>
+        <v>-2.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>-2.17</v>
+        <v>28</v>
       </c>
       <c r="AF14" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI14" t="n">
-        <v>3</v>
+        <v>2.545300000000001</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.545300000000001</v>
+        <v>6.478552090000005</v>
       </c>
       <c r="AK14" t="n">
-        <v>6.478552090000005</v>
+        <v>84.5977</v>
       </c>
       <c r="AL14" t="n">
-        <v>84.5977</v>
+        <v>2.12</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.12</v>
+        <v>11</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AO14" t="n">
-        <v>6</v>
+        <v>34.75893299999999</v>
       </c>
       <c r="AP14" t="n">
-        <v>34.75893299999999</v>
+        <v>29</v>
       </c>
       <c r="AQ14" t="n">
-        <v>29</v>
+        <v>584</v>
       </c>
       <c r="AR14" t="n">
-        <v>584</v>
+        <v>1548.11</v>
       </c>
       <c r="AS14" t="n">
-        <v>1548.11</v>
+        <v>2</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
-        <v>4</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.4615384615384615</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>5.857980995127573</v>
       </c>
       <c r="BA14" t="n">
-        <v>47.56</v>
+        <v>4.734000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.857980995127573</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.734000000000001</v>
-      </c>
-      <c r="BD14" t="n">
         <v>0.5882352941176471</v>
       </c>
     </row>
@@ -3061,144 +2973,138 @@
         <v>61.63</v>
       </c>
       <c r="J15" t="n">
-        <v>324.3800000000001</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>4</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>5</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="U15" t="n">
+        <v>13.4806149030278</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.809653314051179</v>
+      </c>
+      <c r="W15" t="n">
+        <v>7.425273066811353</v>
+      </c>
+      <c r="X15" t="n">
+        <v>6.071699104021506</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4.927865493881351</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8.809653314051179</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>7.425273066811353</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>6.071699104021506</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.927865493881351</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.0363000000000002</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.00131769</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>86.0642</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>28.99614</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>556</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1752.05</v>
+      </c>
+      <c r="AS15" t="n">
         <v>4</v>
       </c>
-      <c r="Q15" t="n">
-        <v>5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.5263157894736842</v>
-      </c>
-      <c r="V15" t="n">
-        <v>13.4806149030278</v>
-      </c>
-      <c r="W15" t="n">
-        <v>8.809653314051179</v>
-      </c>
-      <c r="X15" t="n">
-        <v>7.425273066811353</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>6.071699104021506</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.927865493881351</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>8.809653314051179</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>7.425273066811353</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>6.071699104021506</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.927865493881351</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.0363000000000002</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0.00131769</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>86.0642</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>28.99614</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>556</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1752.05</v>
-      </c>
       <c r="AT15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW15" t="n">
-        <v>3</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.4615384615384615</v>
+        <v>3</v>
       </c>
       <c r="AY15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>5.807354922057604</v>
       </c>
       <c r="BA15" t="n">
-        <v>55.73</v>
+        <v>1.272</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.807354922057604</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.272</v>
-      </c>
-      <c r="BD15" t="n">
         <v>0.5263157894736842</v>
       </c>
     </row>
@@ -3239,19 +3145,19 @@
         <v>5.900000000000002</v>
       </c>
       <c r="J16" t="n">
-        <v>277.411</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -3260,123 +3166,117 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3</v>
+        <v>12.97179314295278</v>
       </c>
       <c r="V16" t="n">
-        <v>12.97179314295278</v>
+        <v>7.769385701641229</v>
       </c>
       <c r="W16" t="n">
+        <v>6.024044450132914</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.2035214253293</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.103552222882481</v>
+      </c>
+      <c r="Z16" t="n">
         <v>7.769385701641229</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AA16" t="n">
         <v>6.024044450132914</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
         <v>4.2035214253293</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AC16" t="n">
         <v>3.103552222882481</v>
       </c>
-      <c r="AA16" t="n">
-        <v>7.769385701641229</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>6.024044450132914</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.2035214253293</v>
-      </c>
       <c r="AD16" t="n">
-        <v>3.103552222882481</v>
+        <v>-1.859999999999999</v>
       </c>
       <c r="AE16" t="n">
-        <v>-1.859999999999999</v>
+        <v>21</v>
       </c>
       <c r="AF16" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>1</v>
+        <v>3.3149</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.3149</v>
+        <v>10.98856201</v>
       </c>
       <c r="AK16" t="n">
-        <v>10.98856201</v>
+        <v>89.43310000000001</v>
       </c>
       <c r="AL16" t="n">
-        <v>89.43310000000001</v>
+        <v>3.55</v>
       </c>
       <c r="AM16" t="n">
-        <v>3.55</v>
+        <v>14</v>
       </c>
       <c r="AN16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO16" t="n">
-        <v>12</v>
+        <v>27.12376099999999</v>
       </c>
       <c r="AP16" t="n">
-        <v>27.12376099999999</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>23</v>
+        <v>331</v>
       </c>
       <c r="AR16" t="n">
-        <v>331</v>
+        <v>1696.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>1696.01</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.4444444444444444</v>
+        <v>3</v>
       </c>
       <c r="AY16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>5.523561956057013</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>4.925999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.523561956057013</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.925999999999999</v>
-      </c>
-      <c r="BD16" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -3417,22 +3317,22 @@
         <v>72.68000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>222.248</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -3447,114 +3347,108 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5</v>
+        <v>9.5199446869934</v>
       </c>
       <c r="V17" t="n">
-        <v>9.5199446869934</v>
+        <v>5.149546493915643</v>
       </c>
       <c r="W17" t="n">
+        <v>4.252339200257269</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.459056231412476</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.705042023310569</v>
+      </c>
+      <c r="Z17" t="n">
         <v>5.149546493915643</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AA17" t="n">
         <v>4.252339200257269</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
         <v>2.459056231412476</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AC17" t="n">
         <v>1.705042023310569</v>
       </c>
-      <c r="AA17" t="n">
-        <v>5.149546493915643</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>4.252339200257269</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.459056231412476</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.705042023310569</v>
+        <v>-1.85</v>
       </c>
       <c r="AE17" t="n">
-        <v>-1.85</v>
+        <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI17" t="n">
-        <v>5</v>
+        <v>1.808100000000001</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.808100000000001</v>
+        <v>3.269225610000005</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.269225610000005</v>
+        <v>58.3359</v>
       </c>
       <c r="AL17" t="n">
-        <v>58.3359</v>
+        <v>1.9</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.9</v>
+        <v>11</v>
       </c>
       <c r="AN17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>23.160898</v>
       </c>
       <c r="AP17" t="n">
-        <v>23.160898</v>
+        <v>17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="AR17" t="n">
-        <v>178</v>
+        <v>721.0599999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>721.0599999999999</v>
+        <v>3</v>
       </c>
       <c r="AT17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV17" t="n">
         <v>3</v>
       </c>
       <c r="AW17" t="n">
-        <v>3</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.4285714285714285</v>
+        <v>2</v>
       </c>
       <c r="AY17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>5.08746284125034</v>
       </c>
       <c r="BA17" t="n">
-        <v>72.68000000000001</v>
+        <v>2.69</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.08746284125034</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="BD17" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3595,144 +3489,138 @@
         <v>218.0899999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>838.0659999999999</v>
+        <v>13</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.9512195121951219</v>
+      </c>
+      <c r="U18" t="n">
+        <v>37.37576598378859</v>
+      </c>
+      <c r="V18" t="n">
+        <v>20.89517218681089</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17.88652017978675</v>
+      </c>
+      <c r="X18" t="n">
+        <v>12.70505004107248</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.019663055438997</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20.89517218681089</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>17.88652017978675</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>12.70505004107248</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.019663055438997</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-1.580000000000001</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>58</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-0.0816000000000021</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.0066585600000003</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>209.4047</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>103.698939</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1784</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>15463.17</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX18" t="n">
         <v>13</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.9512195121951219</v>
-      </c>
-      <c r="V18" t="n">
-        <v>37.37576598378859</v>
-      </c>
-      <c r="W18" t="n">
-        <v>20.89517218681089</v>
-      </c>
-      <c r="X18" t="n">
-        <v>17.88652017978675</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>12.70505004107248</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>9.019663055438997</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>20.89517218681089</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>17.88652017978675</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>12.70505004107248</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>9.019663055438997</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>-1.580000000000001</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>58</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>-0.0816000000000021</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0.0066585600000003</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>209.4047</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>103.698939</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1784</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>15463.17</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AY18" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4</v>
+        <v>6.906890595608519</v>
       </c>
       <c r="BA18" t="n">
-        <v>218.0899999999999</v>
+        <v>1.577</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.906890595608519</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.577</v>
-      </c>
-      <c r="BD18" t="n">
         <v>0.951219512195122</v>
       </c>
     </row>
@@ -3773,28 +3661,28 @@
         <v>208.71</v>
       </c>
       <c r="J19" t="n">
-        <v>828.0060000000001</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -3803,114 +3691,108 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8095238095238095</v>
+        <v>36.05483020766761</v>
       </c>
       <c r="V19" t="n">
-        <v>36.05483020766761</v>
+        <v>20.41075807400902</v>
       </c>
       <c r="W19" t="n">
+        <v>16.9638576816786</v>
+      </c>
+      <c r="X19" t="n">
+        <v>10.91707564739771</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>8.078441232892578</v>
+      </c>
+      <c r="Z19" t="n">
         <v>20.41075807400902</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AA19" t="n">
         <v>16.9638576816786</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AB19" t="n">
         <v>10.91707564739771</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AC19" t="n">
         <v>8.078441232892578</v>
       </c>
-      <c r="AA19" t="n">
-        <v>20.41075807400902</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>16.9638576816786</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>10.91707564739771</v>
-      </c>
       <c r="AD19" t="n">
-        <v>8.078441232892578</v>
+        <v>-2.8</v>
       </c>
       <c r="AE19" t="n">
-        <v>-2.8</v>
+        <v>58</v>
       </c>
       <c r="AF19" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="AG19" t="n">
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AI19" t="n">
-        <v>16</v>
+        <v>1.500899999999995</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.500899999999995</v>
+        <v>2.252700809999984</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.252700809999984</v>
+        <v>208.1323</v>
       </c>
       <c r="AL19" t="n">
-        <v>208.1323</v>
+        <v>4.32</v>
       </c>
       <c r="AM19" t="n">
-        <v>4.32</v>
+        <v>4</v>
       </c>
       <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>96.57128300000004</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>2072</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>13335.16</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU19" t="n">
         <v>4</v>
       </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>96.57128300000004</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2072</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>13335.16</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3</v>
-      </c>
       <c r="AV19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.4782608695652174</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3</v>
+        <v>6.906890595608519</v>
       </c>
       <c r="BA19" t="n">
-        <v>202.81</v>
+        <v>2.951</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.906890595608519</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.951</v>
-      </c>
-      <c r="BD19" t="n">
         <v>0.8095238095238095</v>
       </c>
     </row>
@@ -3951,7 +3833,7 @@
         <v>44.59</v>
       </c>
       <c r="J20" t="n">
-        <v>299.3700000000001</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -3960,135 +3842,129 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="U20" t="n">
+        <v>12.95104626900429</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.102093592364023</v>
+      </c>
+      <c r="W20" t="n">
+        <v>7.113244797870749</v>
+      </c>
+      <c r="X20" t="n">
+        <v>6.354309691044521</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>5.388740830926851</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8.102093592364023</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7.113244797870749</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.354309691044521</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.388740830926851</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="n">
         <v>4</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="V20" t="n">
-        <v>12.95104626900429</v>
-      </c>
-      <c r="W20" t="n">
-        <v>8.102093592364023</v>
-      </c>
-      <c r="X20" t="n">
-        <v>7.113244797870749</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>6.354309691044521</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.388740830926851</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>8.102093592364023</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>7.113244797870749</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>6.354309691044521</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>5.388740830926851</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1</v>
-      </c>
       <c r="AI20" t="n">
-        <v>4</v>
+        <v>0.1806999999999972</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.1806999999999972</v>
+        <v>0.0326524899999989</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.0326524899999989</v>
+        <v>81.70570000000001</v>
       </c>
       <c r="AL20" t="n">
-        <v>81.70570000000001</v>
+        <v>3</v>
       </c>
       <c r="AM20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO20" t="n">
-        <v>6</v>
+        <v>28.769347</v>
       </c>
       <c r="AP20" t="n">
-        <v>28.769347</v>
+        <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>26</v>
+        <v>328</v>
       </c>
       <c r="AR20" t="n">
-        <v>328</v>
+        <v>1747.04</v>
       </c>
       <c r="AS20" t="n">
-        <v>1747.04</v>
+        <v>1</v>
       </c>
       <c r="AT20" t="n">
         <v>1</v>
       </c>
       <c r="AU20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW20" t="n">
-        <v>2</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.4444444444444444</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>5.700439718141093</v>
       </c>
       <c r="BA20" t="n">
-        <v>38.69</v>
+        <v>0.8109999999999997</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.700439718141093</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0.8109999999999997</v>
-      </c>
-      <c r="BD20" t="n">
         <v>0.5555555555555556</v>
       </c>
     </row>
@@ -4129,144 +4005,138 @@
         <v>55.59</v>
       </c>
       <c r="J21" t="n">
-        <v>285.343</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="U21" t="n">
+        <v>11.99001157404039</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.713327954418207</v>
+      </c>
+      <c r="W21" t="n">
+        <v>6.930110293573662</v>
+      </c>
+      <c r="X21" t="n">
+        <v>6.149738248658419</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>5.238415570709245</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7.713327954418207</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>6.930110293573662</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>6.149738248658419</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.238415570709245</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH21" t="n">
         <v>4</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="V21" t="n">
-        <v>11.99001157404039</v>
-      </c>
-      <c r="W21" t="n">
-        <v>7.713327954418207</v>
-      </c>
-      <c r="X21" t="n">
-        <v>6.930110293573662</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>6.149738248658419</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.238415570709245</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>7.713327954418207</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>6.930110293573662</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>6.149738248658419</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>5.238415570709245</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2</v>
-      </c>
       <c r="AI21" t="n">
-        <v>4</v>
+        <v>-0.0703000000000024</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-0.0703000000000024</v>
+        <v>0.0049420900000003</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.0049420900000003</v>
+        <v>76.93660000000001</v>
       </c>
       <c r="AL21" t="n">
-        <v>76.93660000000001</v>
+        <v>2.89</v>
       </c>
       <c r="AM21" t="n">
-        <v>2.89</v>
+        <v>8</v>
       </c>
       <c r="AN21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO21" t="n">
-        <v>6</v>
+        <v>24.666933</v>
       </c>
       <c r="AP21" t="n">
-        <v>24.666933</v>
+        <v>25</v>
       </c>
       <c r="AQ21" t="n">
-        <v>25</v>
+        <v>289</v>
       </c>
       <c r="AR21" t="n">
-        <v>289</v>
+        <v>1516.04</v>
       </c>
       <c r="AS21" t="n">
-        <v>1516.04</v>
+        <v>2</v>
       </c>
       <c r="AT21" t="n">
         <v>2</v>
       </c>
       <c r="AU21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>5.643856189774724</v>
       </c>
       <c r="BA21" t="n">
-        <v>49.69</v>
+        <v>0.49</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.643856189774724</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="BD21" t="n">
         <v>0.5294117647058824</v>
       </c>
     </row>
@@ -4307,144 +4177,138 @@
         <v>11.8</v>
       </c>
       <c r="J22" t="n">
-        <v>390.9580000000002</v>
+        <v>5</v>
       </c>
       <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="U22" t="n">
+        <v>17.1467582846151</v>
+      </c>
+      <c r="V22" t="n">
+        <v>10.39060610174289</v>
+      </c>
+      <c r="W22" t="n">
+        <v>8.102376583634639</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5.813725456567711</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>4.268826550418588</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>10.01264162873366</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>7.665940803162654</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>5.561749141228225</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.142838392748846</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-2.129999999999999</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>3.293000000000001</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>10.84384900000001</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>113.5962</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>33.89658899999999</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>31</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>669</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2608.03</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX22" t="n">
         <v>5</v>
       </c>
-      <c r="L22" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="V22" t="n">
-        <v>17.1467582846151</v>
-      </c>
-      <c r="W22" t="n">
-        <v>10.39060610174289</v>
-      </c>
-      <c r="X22" t="n">
-        <v>8.102376583634639</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>5.813725456567711</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.268826550418588</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>10.01264162873366</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>7.665940803162654</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>5.561749141228225</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.142838392748846</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>-2.129999999999999</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>3.293000000000001</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>10.84384900000001</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>113.5962</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>33.89658899999999</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>31</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>669</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2608.03</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AY22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1</v>
+        <v>5.954196310386876</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.954196310386876</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="BD22" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -4485,13 +4349,13 @@
         <v>89.72999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>335.4240000000001</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -4506,123 +4370,117 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5555555555555556</v>
+        <v>14.83435053308583</v>
       </c>
       <c r="V23" t="n">
-        <v>14.83435053308583</v>
+        <v>8.253564278601154</v>
       </c>
       <c r="W23" t="n">
+        <v>5.989025320239127</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.232206931589729</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.030453419649927</v>
+      </c>
+      <c r="Z23" t="n">
         <v>8.253564278601154</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AA23" t="n">
         <v>5.989025320239127</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AB23" t="n">
         <v>3.232206931589729</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AC23" t="n">
         <v>2.030453419649927</v>
       </c>
-      <c r="AA23" t="n">
-        <v>8.253564278601154</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>5.989025320239127</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.232206931589729</v>
-      </c>
       <c r="AD23" t="n">
-        <v>2.030453419649927</v>
+        <v>-1.92</v>
       </c>
       <c r="AE23" t="n">
-        <v>-1.92</v>
+        <v>24</v>
       </c>
       <c r="AF23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.5919000000000014</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.3503456100000017</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>89.7872</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>35.32858899999999</v>
+      </c>
+      <c r="AP23" t="n">
         <v>24</v>
       </c>
-      <c r="AG23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI23" t="n">
+      <c r="AQ23" t="n">
+        <v>522</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2049.06</v>
+      </c>
+      <c r="AS23" t="n">
         <v>4</v>
       </c>
-      <c r="AJ23" t="n">
-        <v>0.5919000000000014</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0.3503456100000017</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>89.7872</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>35.32858899999999</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>522</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2049.06</v>
-      </c>
       <c r="AT23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU23" t="n">
         <v>4</v>
       </c>
-      <c r="AU23" t="n">
-        <v>2</v>
-      </c>
       <c r="AV23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW23" t="n">
-        <v>7</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.4666666666666667</v>
+        <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>5.584962500721157</v>
       </c>
       <c r="BA23" t="n">
-        <v>75.63</v>
+        <v>1.827</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.584962500721157</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.827</v>
-      </c>
-      <c r="BD23" t="n">
         <v>0.5555555555555556</v>
       </c>
     </row>
@@ -4663,22 +4521,22 @@
         <v>115.04</v>
       </c>
       <c r="J24" t="n">
-        <v>222.251</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -4693,114 +4551,108 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="U24" t="n">
-        <v>0.25</v>
+        <v>8.146012074364309</v>
       </c>
       <c r="V24" t="n">
-        <v>8.146012074364309</v>
+        <v>5.395561829005821</v>
       </c>
       <c r="W24" t="n">
-        <v>5.395561829005821</v>
+        <v>4.811973693691262</v>
       </c>
       <c r="X24" t="n">
-        <v>4.811973693691262</v>
+        <v>3.081509512109847</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.081509512109847</v>
+        <v>1.905360262383568</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.905360262383568</v>
+        <v>3.032745770156533</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.032745770156533</v>
+        <v>2.099317642379012</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.099317642379012</v>
+        <v>0.9328171861807086</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.9328171861807086</v>
+        <v>0.5258473654376647</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.5258473654376647</v>
+        <v>-1.06</v>
       </c>
       <c r="AE24" t="n">
-        <v>-1.06</v>
+        <v>13</v>
       </c>
       <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>-1.3288</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.765709440000001</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>47.61360000000001</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>17.593242</v>
+      </c>
+      <c r="AP24" t="n">
         <v>13</v>
       </c>
-      <c r="AG24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>-1.3288</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.765709440000001</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>47.61360000000001</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>17.593242</v>
-      </c>
       <c r="AQ24" t="n">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="AR24" t="n">
-        <v>140</v>
+        <v>205.09</v>
       </c>
       <c r="AS24" t="n">
-        <v>205.09</v>
+        <v>7</v>
       </c>
       <c r="AT24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="n">
         <v>2</v>
       </c>
       <c r="AV24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>3</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.4285714285714285</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>4.700439718141093</v>
       </c>
       <c r="BA24" t="n">
-        <v>151.66</v>
+        <v>-0.9810000000000002</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.700439718141093</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>-0.9810000000000002</v>
-      </c>
-      <c r="BD24" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -4841,13 +4693,13 @@
         <v>66.43000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>179.151</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -4862,123 +4714,117 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1111111111111111</v>
+        <v>6.942394238613956</v>
       </c>
       <c r="V25" t="n">
-        <v>6.942394238613956</v>
+        <v>3.597970995349284</v>
       </c>
       <c r="W25" t="n">
+        <v>2.377260592477454</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.36065984447708</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.8791235919194019</v>
+      </c>
+      <c r="Z25" t="n">
         <v>3.597970995349284</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AA25" t="n">
         <v>2.377260592477454</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AB25" t="n">
         <v>1.36065984447708</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AC25" t="n">
         <v>0.8791235919194019</v>
       </c>
-      <c r="AA25" t="n">
-        <v>3.597970995349284</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.377260592477454</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.36065984447708</v>
-      </c>
       <c r="AD25" t="n">
-        <v>0.8791235919194019</v>
+        <v>-1.84</v>
       </c>
       <c r="AE25" t="n">
-        <v>-1.84</v>
+        <v>13</v>
       </c>
       <c r="AF25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.5242999999999998</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.2748904899999997</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>41.67100000000001</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>12.442449</v>
+      </c>
+      <c r="AP25" t="n">
         <v>13</v>
       </c>
-      <c r="AG25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0.5242999999999998</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0.2748904899999997</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>41.67100000000001</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>12.442449</v>
-      </c>
       <c r="AQ25" t="n">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="AR25" t="n">
-        <v>123</v>
+        <v>244.04</v>
       </c>
       <c r="AS25" t="n">
-        <v>244.04</v>
+        <v>3</v>
       </c>
       <c r="AT25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW25" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AY25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>4.700439718141093</v>
       </c>
       <c r="BA25" t="n">
-        <v>66.43000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.700439718141093</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="BD25" t="n">
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -5019,144 +4865,138 @@
         <v>49.36</v>
       </c>
       <c r="J26" t="n">
-        <v>325.4280000000001</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="U26" t="n">
+        <v>15.26619675571897</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7.830021802918163</v>
+      </c>
+      <c r="W26" t="n">
+        <v>5.869924108262884</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.905106652756213</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.389679870057566</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>7.830021802918163</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>5.869924108262884</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>3.905106652756213</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.389679870057566</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>4.9628</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>24.62938384</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>101.9638</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN26" t="n">
         <v>6</v>
       </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="V26" t="n">
-        <v>15.26619675571897</v>
-      </c>
-      <c r="W26" t="n">
-        <v>7.830021802918163</v>
-      </c>
-      <c r="X26" t="n">
-        <v>5.869924108262884</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>3.905106652756213</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.389679870057566</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>7.830021802918163</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>5.869924108262884</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.905106652756213</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.389679870057566</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="AF26" t="n">
+      <c r="AO26" t="n">
+        <v>31.162175</v>
+      </c>
+      <c r="AP26" t="n">
         <v>24</v>
       </c>
-      <c r="AG26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>4.9628</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>24.62938384</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>101.9638</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO26" t="n">
+      <c r="AQ26" t="n">
+        <v>549</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1849.03</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="AX26" t="n">
         <v>6</v>
       </c>
-      <c r="AP26" t="n">
-        <v>31.162175</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>549</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1849.03</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0.4666666666666667</v>
-      </c>
       <c r="AY26" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1</v>
+        <v>5.584962500721157</v>
       </c>
       <c r="BA26" t="n">
-        <v>49.36</v>
+        <v>5.309000000000002</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.584962500721157</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>5.309000000000002</v>
-      </c>
-      <c r="BD26" t="n">
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -5197,144 +5037,138 @@
         <v>58.92</v>
       </c>
       <c r="J27" t="n">
-        <v>347.438</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="U27" t="n">
+        <v>15.01996036975664</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8.97713635249818</v>
+      </c>
+      <c r="W27" t="n">
+        <v>6.591601355842868</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4.551625319006162</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>3.1367251692738</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>8.97713635249818</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>6.591601355842868</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>4.551625319006162</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.1367251692738</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.440900000000003</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>5.957992810000014</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>100.878</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>30.35976099999999</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>521</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1951.04</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX27" t="n">
         <v>6</v>
       </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="V27" t="n">
-        <v>15.01996036975664</v>
-      </c>
-      <c r="W27" t="n">
-        <v>8.97713635249818</v>
-      </c>
-      <c r="X27" t="n">
-        <v>6.591601355842868</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>4.551625319006162</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.1367251692738</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>8.97713635249818</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>6.591601355842868</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.551625319006162</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3.1367251692738</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>-2.72</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>2.440900000000003</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>5.957992810000014</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>100.878</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>30.35976099999999</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>521</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1951.04</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AY27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>5.807354922057604</v>
       </c>
       <c r="BA27" t="n">
-        <v>53.02</v>
+        <v>3.508</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.807354922057604</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>3.508</v>
-      </c>
-      <c r="BD27" t="n">
         <v>0.2727272727272727</v>
       </c>
     </row>
@@ -5375,144 +5209,138 @@
         <v>119.05</v>
       </c>
       <c r="J28" t="n">
-        <v>225.208</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="U28" t="n">
+        <v>8.381371844866454</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.613430051544285</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3.09972151534539</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.97477809087899</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.306785380568755</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.613430051544285</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.09972151534539</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.97477809087899</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.306785380568755</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>-1.3591</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.84715281</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>54.10850000000001</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>19.519277</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>239</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>544.08</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AX28" t="n">
         <v>4</v>
       </c>
-      <c r="L28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="V28" t="n">
-        <v>8.381371844866454</v>
-      </c>
-      <c r="W28" t="n">
-        <v>4.613430051544285</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.09972151534539</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.97477809087899</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.306785380568755</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4.613430051544285</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>3.09972151534539</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.97477809087899</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.306785380568755</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>-1.93</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-1.3591</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.84715281</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>54.10850000000001</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>19.519277</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>239</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>544.08</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0.4444444444444444</v>
-      </c>
       <c r="AY28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>5.08746284125034</v>
       </c>
       <c r="BA28" t="n">
-        <v>119.05</v>
+        <v>0.4629999999999999</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.08746284125034</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0.4629999999999999</v>
-      </c>
-      <c r="BD28" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -5553,144 +5381,138 @@
         <v>91.85000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>448.4290000000002</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2083333333333333</v>
+        <v>17.34689415136274</v>
       </c>
       <c r="V29" t="n">
-        <v>17.34689415136274</v>
+        <v>10.44602647399025</v>
       </c>
       <c r="W29" t="n">
+        <v>7.991436925271519</v>
+      </c>
+      <c r="X29" t="n">
+        <v>6.015781180354416</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>4.456672527600188</v>
+      </c>
+      <c r="Z29" t="n">
         <v>10.44602647399025</v>
       </c>
-      <c r="X29" t="n">
+      <c r="AA29" t="n">
         <v>7.991436925271519</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AB29" t="n">
         <v>6.015781180354416</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AC29" t="n">
         <v>4.456672527600188</v>
       </c>
-      <c r="AA29" t="n">
-        <v>10.44602647399025</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>7.991436925271519</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>6.015781180354416</v>
-      </c>
       <c r="AD29" t="n">
-        <v>4.456672527600188</v>
+        <v>-3.849999999999999</v>
       </c>
       <c r="AE29" t="n">
-        <v>-3.849999999999999</v>
+        <v>33</v>
       </c>
       <c r="AF29" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="AG29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>3.845499999999999</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>14.78787024999999</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>116.0037</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>3.109999999999999</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>31.131726</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>781</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2080.09</v>
+      </c>
+      <c r="AS29" t="n">
         <v>6</v>
       </c>
-      <c r="AH29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>3.845499999999999</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>14.78787024999999</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>116.0037</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>3.109999999999999</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>31.131726</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>38</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>781</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2080.09</v>
-      </c>
       <c r="AT29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AY29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>6.247927513443585</v>
       </c>
       <c r="BA29" t="n">
-        <v>91.84999999999999</v>
+        <v>2.815</v>
       </c>
       <c r="BB29" t="n">
-        <v>6.247927513443585</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2.815</v>
-      </c>
-      <c r="BD29" t="n">
         <v>0.2083333333333333</v>
       </c>
     </row>
@@ -5731,13 +5553,13 @@
         <v>93.34999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>322.364</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -5752,123 +5574,117 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="U30" t="n">
-        <v>0.1578947368421053</v>
+        <v>13.06736184323002</v>
       </c>
       <c r="V30" t="n">
-        <v>13.06736184323002</v>
+        <v>7.558119063093586</v>
       </c>
       <c r="W30" t="n">
+        <v>5.263020614265233</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.446161666062129</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.179837655232092</v>
+      </c>
+      <c r="Z30" t="n">
         <v>7.558119063093586</v>
       </c>
-      <c r="X30" t="n">
+      <c r="AA30" t="n">
         <v>5.263020614265233</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AB30" t="n">
         <v>3.446161666062129</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AC30" t="n">
         <v>2.179837655232092</v>
       </c>
-      <c r="AA30" t="n">
-        <v>7.558119063093586</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>5.263020614265233</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.446161666062129</v>
-      </c>
       <c r="AD30" t="n">
-        <v>2.179837655232092</v>
+        <v>-3.259999999999999</v>
       </c>
       <c r="AE30" t="n">
-        <v>-3.259999999999999</v>
+        <v>24</v>
       </c>
       <c r="AF30" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI30" t="n">
-        <v>4</v>
+        <v>3.171100000000002</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.171100000000002</v>
+        <v>10.05587521000001</v>
       </c>
       <c r="AK30" t="n">
-        <v>10.05587521000001</v>
+        <v>92.1888</v>
       </c>
       <c r="AL30" t="n">
-        <v>92.1888</v>
+        <v>3</v>
       </c>
       <c r="AM30" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AN30" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
-        <v>12</v>
+        <v>21.95572599999999</v>
       </c>
       <c r="AP30" t="n">
-        <v>21.95572599999999</v>
+        <v>25</v>
       </c>
       <c r="AQ30" t="n">
-        <v>25</v>
+        <v>578</v>
       </c>
       <c r="AR30" t="n">
-        <v>578</v>
+        <v>1297.05</v>
       </c>
       <c r="AS30" t="n">
-        <v>1297.05</v>
+        <v>5</v>
       </c>
       <c r="AT30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU30" t="n">
         <v>3</v>
       </c>
       <c r="AV30" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AW30" t="n">
-        <v>8</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.4666666666666667</v>
+        <v>7</v>
       </c>
       <c r="AY30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>5.643856189774724</v>
       </c>
       <c r="BA30" t="n">
-        <v>93.34999999999999</v>
+        <v>2.915</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.643856189774724</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.915</v>
-      </c>
-      <c r="BD30" t="n">
         <v>0.1578947368421052</v>
       </c>
     </row>
@@ -5909,144 +5725,138 @@
         <v>23.47</v>
       </c>
       <c r="J31" t="n">
-        <v>247.382</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="U31" t="n">
+        <v>11.65357573606425</v>
+      </c>
+      <c r="V31" t="n">
+        <v>7.296095079874477</v>
+      </c>
+      <c r="W31" t="n">
+        <v>5.34740718354015</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.972997747869123</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>3.113835438979122</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>7.296095079874477</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>5.34740718354015</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>3.972997747869123</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.113835438979122</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4.262</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>18.164644</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>77.17420000000001</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>29.310175</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>261</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1630.02</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AX31" t="n">
         <v>5</v>
       </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="V31" t="n">
-        <v>11.65357573606425</v>
-      </c>
-      <c r="W31" t="n">
-        <v>7.296095079874477</v>
-      </c>
-      <c r="X31" t="n">
-        <v>5.34740718354015</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>3.972997747869123</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.113835438979122</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>7.296095079874477</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>5.34740718354015</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.972997747869123</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.113835438979122</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>4.262</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>18.164644</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>77.17420000000001</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>29.310175</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>261</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1630.02</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0.4444444444444444</v>
-      </c>
       <c r="AY31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>5.247927513443585</v>
       </c>
       <c r="BA31" t="n">
-        <v>23.47</v>
+        <v>3.328</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.247927513443585</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>3.328</v>
-      </c>
-      <c r="BD31" t="n">
         <v>0.625</v>
       </c>
     </row>
@@ -6087,144 +5897,138 @@
         <v>117</v>
       </c>
       <c r="J32" t="n">
-        <v>418.4460000000003</v>
+        <v>8</v>
       </c>
       <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="U32" t="n">
+        <v>17.68326680625785</v>
+      </c>
+      <c r="V32" t="n">
+        <v>9.46864571760643</v>
+      </c>
+      <c r="W32" t="n">
+        <v>7.070241172606365</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.477906014587668</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>3.259418368547829</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>9.46864571760643</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>7.070241172606365</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>4.477906014587668</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.259418368547829</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH32" t="n">
         <v>8</v>
       </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="V32" t="n">
-        <v>17.68326680625785</v>
-      </c>
-      <c r="W32" t="n">
-        <v>9.46864571760643</v>
-      </c>
-      <c r="X32" t="n">
-        <v>7.070241172606365</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>4.477906014587668</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.259418368547829</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>9.46864571760643</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>7.070241172606365</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>4.477906014587668</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.259418368547829</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1</v>
-      </c>
       <c r="AI32" t="n">
-        <v>8</v>
+        <v>2.361799999999998</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.361799999999998</v>
+        <v>5.578099239999992</v>
       </c>
       <c r="AK32" t="n">
-        <v>5.578099239999992</v>
+        <v>112.3732</v>
       </c>
       <c r="AL32" t="n">
-        <v>112.3732</v>
+        <v>2.78</v>
       </c>
       <c r="AM32" t="n">
-        <v>2.78</v>
+        <v>11</v>
       </c>
       <c r="AN32" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AO32" t="n">
+        <v>38.003382</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>31</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>565</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2379.09</v>
+      </c>
+      <c r="AS32" t="n">
         <v>6</v>
       </c>
-      <c r="AP32" t="n">
-        <v>38.003382</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>31</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>565</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2379.09</v>
-      </c>
       <c r="AT32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW32" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="AY32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>5.954196310386876</v>
       </c>
       <c r="BA32" t="n">
-        <v>117</v>
+        <v>3.997999999999999</v>
       </c>
       <c r="BB32" t="n">
-        <v>5.954196310386876</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>3.997999999999999</v>
-      </c>
-      <c r="BD32" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
@@ -6265,13 +6069,13 @@
         <v>9.23</v>
       </c>
       <c r="J33" t="n">
-        <v>643.587</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
         <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -6286,10 +6090,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6298,79 +6102,79 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>18.50141543996595</v>
       </c>
       <c r="V33" t="n">
-        <v>18.50141543996595</v>
+        <v>9.60953240359416</v>
       </c>
       <c r="W33" t="n">
-        <v>9.60953240359416</v>
+        <v>8.621561061081234</v>
       </c>
       <c r="X33" t="n">
-        <v>8.621561061081234</v>
+        <v>7.09744261425531</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.09744261425531</v>
+        <v>4.078037253507229</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.078037253507229</v>
+        <v>4.851542786250048</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.851542786250048</v>
+        <v>3.495539666034109</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.495539666034109</v>
+        <v>2.169532982849794</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.169532982849794</v>
+        <v>1.28352045325648</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.28352045325648</v>
+        <v>1.12</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.12</v>
+        <v>19</v>
       </c>
       <c r="AF33" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI33" t="n">
-        <v>1</v>
+        <v>7.8806</v>
       </c>
       <c r="AJ33" t="n">
-        <v>7.8806</v>
+        <v>62.10385636</v>
       </c>
       <c r="AK33" t="n">
-        <v>62.10385636</v>
+        <v>98.03560000000002</v>
       </c>
       <c r="AL33" t="n">
-        <v>98.03560000000002</v>
+        <v>2.01</v>
       </c>
       <c r="AM33" t="n">
-        <v>2.01</v>
+        <v>13</v>
       </c>
       <c r="AN33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO33" t="n">
-        <v>12</v>
+        <v>14.028828</v>
       </c>
       <c r="AP33" t="n">
-        <v>14.028828</v>
+        <v>20</v>
       </c>
       <c r="AQ33" t="n">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="AR33" t="n">
-        <v>304</v>
+        <v>234.07</v>
       </c>
       <c r="AS33" t="n">
-        <v>234.07</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
@@ -6382,27 +6186,21 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AY33" t="n">
         <v>2</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2</v>
+        <v>5.321928094887363</v>
       </c>
       <c r="BA33" t="n">
-        <v>9.23</v>
+        <v>8.291</v>
       </c>
       <c r="BB33" t="n">
-        <v>5.321928094887363</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>8.291</v>
-      </c>
-      <c r="BD33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6443,115 +6241,115 @@
         <v>17.07</v>
       </c>
       <c r="J34" t="n">
-        <v>490.6390000000002</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
         <v>6</v>
       </c>
       <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
         <v>6</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>6</v>
       </c>
       <c r="T34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="U34" t="n">
+        <v>16.74718248074068</v>
+      </c>
+      <c r="V34" t="n">
+        <v>9.373591240370342</v>
+      </c>
+      <c r="W34" t="n">
+        <v>12.03423522128284</v>
+      </c>
+      <c r="X34" t="n">
+        <v>15.305886393855</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>14.04251111291261</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5.593946510278067</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>6.171304027725097</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>6.238044894772958</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>5.638348372554062</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF34" t="n">
         <v>6</v>
       </c>
-      <c r="U34" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V34" t="n">
-        <v>16.74718248074068</v>
-      </c>
-      <c r="W34" t="n">
-        <v>9.373591240370342</v>
-      </c>
-      <c r="X34" t="n">
-        <v>12.03423522128284</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>15.305886393855</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>14.04251111291261</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>5.593946510278067</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>6.171304027725097</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>6.238044894772958</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>5.638348372554062</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>21</v>
-      </c>
       <c r="AG34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1</v>
+        <v>4.4988</v>
       </c>
       <c r="AJ34" t="n">
-        <v>4.4988</v>
+        <v>20.23920144</v>
       </c>
       <c r="AK34" t="n">
-        <v>20.23920144</v>
+        <v>83.19979999999998</v>
       </c>
       <c r="AL34" t="n">
-        <v>83.19979999999998</v>
+        <v>1.35</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AN34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>5.158</v>
       </c>
       <c r="AP34" t="n">
-        <v>5.158</v>
+        <v>25</v>
       </c>
       <c r="AQ34" t="n">
-        <v>25</v>
+        <v>221</v>
       </c>
       <c r="AR34" t="n">
-        <v>221</v>
+        <v>205.11</v>
       </c>
       <c r="AS34" t="n">
-        <v>205.11</v>
+        <v>1</v>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
@@ -6560,27 +6358,21 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>5.643856189774724</v>
       </c>
       <c r="BA34" t="n">
-        <v>17.07</v>
+        <v>3.726000000000001</v>
       </c>
       <c r="BB34" t="n">
-        <v>5.643856189774724</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>3.726000000000001</v>
-      </c>
-      <c r="BD34" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -6621,22 +6413,22 @@
         <v>117.52</v>
       </c>
       <c r="J35" t="n">
-        <v>179.139</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -6654,111 +6446,105 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>6.365624310306893</v>
       </c>
       <c r="V35" t="n">
-        <v>6.365624310306893</v>
+        <v>3.414617842650587</v>
       </c>
       <c r="W35" t="n">
+        <v>2.395831210511147</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.465741058033502</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.9634814617575086</v>
+      </c>
+      <c r="Z35" t="n">
         <v>3.414617842650587</v>
       </c>
-      <c r="X35" t="n">
+      <c r="AA35" t="n">
         <v>2.395831210511147</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AB35" t="n">
         <v>1.465741058033502</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AC35" t="n">
         <v>0.9634814617575086</v>
       </c>
-      <c r="AA35" t="n">
-        <v>3.414617842650587</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>2.395831210511147</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.465741058033502</v>
-      </c>
       <c r="AD35" t="n">
-        <v>0.9634814617575086</v>
+        <v>-2.18</v>
       </c>
       <c r="AE35" t="n">
-        <v>-2.18</v>
+        <v>13</v>
       </c>
       <c r="AF35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>-0.7852999999999999</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.6166960899999998</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>41.7305</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM35" t="n">
         <v>13</v>
       </c>
-      <c r="AG35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI35" t="n">
+      <c r="AN35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>10.682035</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>134</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>205.07</v>
+      </c>
+      <c r="AS35" t="n">
         <v>5</v>
       </c>
-      <c r="AJ35" t="n">
-        <v>-0.7852999999999999</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0.6166960899999998</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>41.7305</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>10.682035</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>134</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>205.07</v>
-      </c>
       <c r="AT35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
         <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>4.807354922057604</v>
       </c>
       <c r="BA35" t="n">
-        <v>117.52</v>
+        <v>-1.117</v>
       </c>
       <c r="BB35" t="n">
-        <v>4.807354922057604</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>-1.117</v>
-      </c>
-      <c r="BD35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6799,31 +6585,31 @@
         <v>63.83</v>
       </c>
       <c r="J36" t="n">
-        <v>160.18</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -6832,111 +6618,105 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>6.358528806137672</v>
       </c>
       <c r="V36" t="n">
-        <v>6.358528806137672</v>
+        <v>3.586506225876393</v>
       </c>
       <c r="W36" t="n">
+        <v>2.424764312408268</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.707184566803188</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.134526722021128</v>
+      </c>
+      <c r="Z36" t="n">
         <v>3.586506225876393</v>
       </c>
-      <c r="X36" t="n">
+      <c r="AA36" t="n">
         <v>2.424764312408268</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AB36" t="n">
         <v>1.707184566803188</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AC36" t="n">
         <v>1.134526722021128</v>
       </c>
-      <c r="AA36" t="n">
-        <v>3.586506225876393</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.424764312408268</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.707184566803188</v>
-      </c>
       <c r="AD36" t="n">
-        <v>1.134526722021128</v>
+        <v>-1.68</v>
       </c>
       <c r="AE36" t="n">
-        <v>-1.68</v>
+        <v>12</v>
       </c>
       <c r="AF36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.7704000000000002</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.5935161600000003</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>50.3093</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM36" t="n">
         <v>12</v>
       </c>
-      <c r="AG36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI36" t="n">
+      <c r="AN36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>8.745655999999999</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>119</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>309.04</v>
+      </c>
+      <c r="AS36" t="n">
         <v>4</v>
       </c>
-      <c r="AJ36" t="n">
-        <v>0.7704000000000002</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0.5935161600000003</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>50.3093</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>8.745655999999999</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>119</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>309.04</v>
-      </c>
       <c r="AT36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW36" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AY36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>4.700439718141093</v>
       </c>
       <c r="BA36" t="n">
-        <v>63.83</v>
+        <v>0.6880000000000006</v>
       </c>
       <c r="BB36" t="n">
-        <v>4.700439718141093</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>0.6880000000000006</v>
-      </c>
-      <c r="BD36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6977,19 +6757,19 @@
         <v>3.24</v>
       </c>
       <c r="J37" t="n">
-        <v>277.411</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -6998,123 +6778,117 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="U37" t="n">
-        <v>0.3</v>
+        <v>12.97179314295278</v>
       </c>
       <c r="V37" t="n">
-        <v>12.97179314295278</v>
+        <v>7.769385701641229</v>
       </c>
       <c r="W37" t="n">
+        <v>6.024044450132914</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.2035214253293</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>3.103552222882481</v>
+      </c>
+      <c r="Z37" t="n">
         <v>7.769385701641229</v>
       </c>
-      <c r="X37" t="n">
+      <c r="AA37" t="n">
         <v>6.024044450132914</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AB37" t="n">
         <v>4.2035214253293</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AC37" t="n">
         <v>3.103552222882481</v>
       </c>
-      <c r="AA37" t="n">
-        <v>7.769385701641229</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>6.024044450132914</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>4.2035214253293</v>
-      </c>
       <c r="AD37" t="n">
-        <v>3.103552222882481</v>
+        <v>-1.859999999999999</v>
       </c>
       <c r="AE37" t="n">
-        <v>-1.859999999999999</v>
+        <v>21</v>
       </c>
       <c r="AF37" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AG37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI37" t="n">
-        <v>1</v>
+        <v>4.772</v>
       </c>
       <c r="AJ37" t="n">
-        <v>4.772</v>
+        <v>22.771984</v>
       </c>
       <c r="AK37" t="n">
-        <v>22.771984</v>
+        <v>92.33110000000001</v>
       </c>
       <c r="AL37" t="n">
-        <v>92.33110000000001</v>
+        <v>3.55</v>
       </c>
       <c r="AM37" t="n">
-        <v>3.55</v>
+        <v>14</v>
       </c>
       <c r="AN37" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO37" t="n">
-        <v>12</v>
+        <v>27.12376099999999</v>
       </c>
       <c r="AP37" t="n">
-        <v>27.12376099999999</v>
+        <v>23</v>
       </c>
       <c r="AQ37" t="n">
-        <v>23</v>
+        <v>331</v>
       </c>
       <c r="AR37" t="n">
-        <v>331</v>
+        <v>1696.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>1696.01</v>
+        <v>1</v>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW37" t="n">
-        <v>5</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.4444444444444444</v>
+        <v>3</v>
       </c>
       <c r="AY37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>5.523561956057013</v>
       </c>
       <c r="BA37" t="n">
-        <v>3.24</v>
+        <v>4.925999999999999</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.523561956057013</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>4.925999999999999</v>
-      </c>
-      <c r="BD37" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -7155,22 +6929,22 @@
         <v>50.08000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>370.888</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
         <v>3</v>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -7179,120 +6953,114 @@
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="U38" t="n">
-        <v>0.4210526315789473</v>
+        <v>16.16210997471867</v>
       </c>
       <c r="V38" t="n">
-        <v>16.16210997471867</v>
+        <v>9.392217365223972</v>
       </c>
       <c r="W38" t="n">
-        <v>9.392217365223972</v>
+        <v>7.069424296329509</v>
       </c>
       <c r="X38" t="n">
-        <v>7.069424296329509</v>
+        <v>5.375519712990235</v>
       </c>
       <c r="Y38" t="n">
-        <v>5.375519712990235</v>
+        <v>3.752574322000269</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.752574322000269</v>
+        <v>9.014252892214746</v>
       </c>
       <c r="AA38" t="n">
-        <v>9.014252892214746</v>
+        <v>6.662224169588903</v>
       </c>
       <c r="AB38" t="n">
-        <v>6.662224169588903</v>
+        <v>5.04593149195019</v>
       </c>
       <c r="AC38" t="n">
-        <v>5.04593149195019</v>
+        <v>3.532325520947215</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.532325520947215</v>
+        <v>-2.18</v>
       </c>
       <c r="AE38" t="n">
-        <v>-2.18</v>
+        <v>26</v>
       </c>
       <c r="AF38" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="AG38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI38" t="n">
-        <v>6</v>
+        <v>3.426100000000003</v>
       </c>
       <c r="AJ38" t="n">
-        <v>3.426100000000003</v>
+        <v>11.73816121000002</v>
       </c>
       <c r="AK38" t="n">
-        <v>11.73816121000002</v>
+        <v>104.0383</v>
       </c>
       <c r="AL38" t="n">
-        <v>104.0383</v>
+        <v>2.78</v>
       </c>
       <c r="AM38" t="n">
-        <v>2.78</v>
+        <v>16</v>
       </c>
       <c r="AN38" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO38" t="n">
-        <v>15</v>
+        <v>35.463761</v>
       </c>
       <c r="AP38" t="n">
-        <v>35.463761</v>
+        <v>29</v>
       </c>
       <c r="AQ38" t="n">
-        <v>29</v>
+        <v>554</v>
       </c>
       <c r="AR38" t="n">
-        <v>554</v>
+        <v>2054.07</v>
       </c>
       <c r="AS38" t="n">
-        <v>2054.07</v>
+        <v>5</v>
       </c>
       <c r="AT38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV38" t="n">
         <v>2</v>
       </c>
       <c r="AW38" t="n">
-        <v>2</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.4615384615384615</v>
+        <v>3</v>
       </c>
       <c r="AY38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>5.857980995127573</v>
       </c>
       <c r="BA38" t="n">
-        <v>50.08000000000001</v>
+        <v>4.069000000000001</v>
       </c>
       <c r="BB38" t="n">
-        <v>5.857980995127573</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>4.069000000000001</v>
-      </c>
-      <c r="BD38" t="n">
         <v>0.4210526315789473</v>
       </c>
     </row>
@@ -7333,13 +7101,13 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>354.491</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
         <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -7354,123 +7122,117 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U39" t="n">
-        <v>0.1428571428571428</v>
+        <v>13.36561951784505</v>
       </c>
       <c r="V39" t="n">
-        <v>13.36561951784505</v>
+        <v>7.343493361445482</v>
       </c>
       <c r="W39" t="n">
-        <v>7.343493361445482</v>
+        <v>7.319538644608238</v>
       </c>
       <c r="X39" t="n">
-        <v>7.319538644608238</v>
+        <v>3.892609990459672</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.892609990459672</v>
+        <v>2.888780652638384</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.888780652638384</v>
+        <v>5.453670996399344</v>
       </c>
       <c r="AA39" t="n">
-        <v>5.453670996399344</v>
+        <v>4.077727698670574</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.077727698670574</v>
+        <v>2.734003689072726</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.734003689072726</v>
+        <v>1.880875391280444</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.880875391280444</v>
+        <v>-0.1100000000000002</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.1100000000000002</v>
+        <v>19</v>
       </c>
       <c r="AF39" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="AG39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>6.3311</v>
       </c>
       <c r="AJ39" t="n">
-        <v>6.3311</v>
+        <v>40.08282721</v>
       </c>
       <c r="AK39" t="n">
-        <v>40.08282721</v>
+        <v>85.31570000000001</v>
       </c>
       <c r="AL39" t="n">
-        <v>85.31570000000001</v>
+        <v>2.45</v>
       </c>
       <c r="AM39" t="n">
-        <v>2.45</v>
+        <v>6</v>
       </c>
       <c r="AN39" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AO39" t="n">
-        <v>12</v>
+        <v>11.938863</v>
       </c>
       <c r="AP39" t="n">
-        <v>11.938863</v>
+        <v>20</v>
       </c>
       <c r="AQ39" t="n">
-        <v>20</v>
+        <v>290</v>
       </c>
       <c r="AR39" t="n">
-        <v>290</v>
+        <v>499.05</v>
       </c>
       <c r="AS39" t="n">
-        <v>499.05</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW39" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AY39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1</v>
+        <v>5.321928094887363</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>6.648000000000001</v>
       </c>
       <c r="BB39" t="n">
-        <v>5.321928094887363</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>6.648000000000001</v>
-      </c>
-      <c r="BD39" t="n">
         <v>0.1428571428571428</v>
       </c>
     </row>
@@ -7511,31 +7273,31 @@
         <v>49.33</v>
       </c>
       <c r="J40" t="n">
-        <v>520.9460000000001</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -7544,111 +7306,105 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>15.78294828953499</v>
       </c>
       <c r="V40" t="n">
-        <v>15.78294828953499</v>
+        <v>8.629508016480081</v>
       </c>
       <c r="W40" t="n">
-        <v>8.629508016480081</v>
+        <v>7.489505785063237</v>
       </c>
       <c r="X40" t="n">
-        <v>7.489505785063237</v>
+        <v>4.994806748626831</v>
       </c>
       <c r="Y40" t="n">
-        <v>4.994806748626831</v>
+        <v>3.851757015894965</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.851757015894965</v>
+        <v>5.964762331777214</v>
       </c>
       <c r="AA40" t="n">
-        <v>5.964762331777214</v>
+        <v>4.535199767527387</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.535199767527387</v>
+        <v>3.114839138772233</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.114839138772233</v>
+        <v>2.138687327311702</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.138687327311702</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.8599999999999999</v>
+        <v>21</v>
       </c>
       <c r="AF40" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AG40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="n">
         <v>2</v>
       </c>
       <c r="AI40" t="n">
-        <v>2</v>
+        <v>4.5387</v>
       </c>
       <c r="AJ40" t="n">
-        <v>4.5387</v>
+        <v>20.59979769</v>
       </c>
       <c r="AK40" t="n">
-        <v>20.59979769</v>
+        <v>97.2983</v>
       </c>
       <c r="AL40" t="n">
-        <v>97.2983</v>
+        <v>2.45</v>
       </c>
       <c r="AM40" t="n">
-        <v>2.45</v>
+        <v>18</v>
       </c>
       <c r="AN40" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AO40" t="n">
-        <v>12</v>
+        <v>16.533656</v>
       </c>
       <c r="AP40" t="n">
-        <v>16.533656</v>
+        <v>23</v>
       </c>
       <c r="AQ40" t="n">
-        <v>23</v>
+        <v>358</v>
       </c>
       <c r="AR40" t="n">
-        <v>358</v>
+        <v>541.0599999999999</v>
       </c>
       <c r="AS40" t="n">
-        <v>541.0599999999999</v>
+        <v>3</v>
       </c>
       <c r="AT40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AY40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2</v>
+        <v>5.523561956057013</v>
       </c>
       <c r="BA40" t="n">
-        <v>49.33</v>
+        <v>5.359</v>
       </c>
       <c r="BB40" t="n">
-        <v>5.523561956057013</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>5.359</v>
-      </c>
-      <c r="BD40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7689,144 +7445,138 @@
         <v>37.38</v>
       </c>
       <c r="J41" t="n">
-        <v>383.4350000000001</v>
+        <v>5</v>
       </c>
       <c r="K41" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="U41" t="n">
+        <v>14.98379130748325</v>
+      </c>
+      <c r="V41" t="n">
+        <v>9.997196573491843</v>
+      </c>
+      <c r="W41" t="n">
+        <v>8.517177380688342</v>
+      </c>
+      <c r="X41" t="n">
+        <v>6.739030530815971</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>4.800615678379732</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>8.557133244691203</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>6.579242400746675</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>4.84439366421956</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.298887000081745</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>4.6771</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>21.87526441</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>94.64530000000001</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>33.92913999999999</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>646</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1654.07</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="AX41" t="n">
         <v>5</v>
       </c>
-      <c r="L41" t="n">
-        <v>2</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" t="n">
-        <v>2</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0.3684210526315789</v>
-      </c>
-      <c r="V41" t="n">
-        <v>14.98379130748325</v>
-      </c>
-      <c r="W41" t="n">
-        <v>9.997196573491843</v>
-      </c>
-      <c r="X41" t="n">
-        <v>8.517177380688342</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>6.739030530815971</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>4.800615678379732</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>8.557133244691203</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>6.579242400746675</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>4.84439366421956</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>3.298887000081745</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>4.6771</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>21.87526441</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>94.64530000000001</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>33.92913999999999</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>646</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>1654.07</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0.4666666666666667</v>
-      </c>
       <c r="AY41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>5.807354922057604</v>
       </c>
       <c r="BA41" t="n">
-        <v>45.76000000000001</v>
+        <v>4.767999999999999</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.807354922057604</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>4.767999999999999</v>
-      </c>
-      <c r="BD41" t="n">
         <v>0.3684210526315789</v>
       </c>
     </row>
@@ -7867,144 +7617,138 @@
         <v>57.61</v>
       </c>
       <c r="J42" t="n">
-        <v>399.434</v>
+        <v>5</v>
       </c>
       <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="U42" t="n">
+        <v>15.35365463379358</v>
+      </c>
+      <c r="V42" t="n">
+        <v>10.05671867163006</v>
+      </c>
+      <c r="W42" t="n">
+        <v>8.756013898450769</v>
+      </c>
+      <c r="X42" t="n">
+        <v>6.892213424745751</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>4.681658770679661</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>8.616655342829414</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>6.818078918509105</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>4.979344924859146</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.240204495409394</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>3.2133</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>10.32529689</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>96.2406</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>33.92914</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>691</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1699.08</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX42" t="n">
         <v>5</v>
       </c>
-      <c r="L42" t="n">
-        <v>2</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.3684210526315789</v>
-      </c>
-      <c r="V42" t="n">
-        <v>15.35365463379358</v>
-      </c>
-      <c r="W42" t="n">
-        <v>10.05671867163006</v>
-      </c>
-      <c r="X42" t="n">
-        <v>8.756013898450769</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>6.892213424745751</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>4.681658770679661</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>8.616655342829414</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>6.818078918509105</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>4.979344924859146</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.240204495409394</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>3.2133</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>10.32529689</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>96.2406</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>33.92914</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>29</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>691</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>1699.08</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AY42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>5.857980995127573</v>
       </c>
       <c r="BA42" t="n">
-        <v>65.99000000000001</v>
+        <v>3.647</v>
       </c>
       <c r="BB42" t="n">
-        <v>5.857980995127573</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>3.647</v>
-      </c>
-      <c r="BD42" t="n">
         <v>0.3684210526315789</v>
       </c>
     </row>
